--- a/Experiments data/K Size/K_Size_PGP_Graph.xlsx
+++ b/Experiments data/K Size/K_Size_PGP_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\SISR Script\Experiments data\K Size\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\K Size\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEDB1C6-AF8B-4D5E-AE79-8B35E57528ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBE1FD6-8BC9-489B-96C7-3976265C143C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="34">
   <si>
     <t>KaMinPar</t>
   </si>
@@ -119,10 +119,25 @@
     <t>Deep Multilevel, ε = 5</t>
   </si>
   <si>
-    <t>Deep Multilevel, ε =  5</t>
+    <t>Deep Multilevel, ε= 0</t>
   </si>
   <si>
-    <t>Deep Multilevel, ε= 0</t>
+    <t>Deep Multilevel, ε = 534</t>
+  </si>
+  <si>
+    <t>Deep Multilevel, ε = 120</t>
+  </si>
+  <si>
+    <t>Deep Multilevel, ε = 22</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε= 0.0</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε = 534</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε =  534</t>
   </si>
 </sst>
 </file>
@@ -674,16 +689,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1593.4</c:v>
+                  <c:v>451</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3205.2</c:v>
+                  <c:v>825.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5889</c:v>
+                  <c:v>1404</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7165.6</c:v>
+                  <c:v>1825.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -704,7 +719,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 0.05</c:v>
+                  <c:v>Deep Multilevel, ε = 534</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -767,16 +782,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>334.6</c:v>
+                  <c:v>422.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1368.4</c:v>
+                  <c:v>759.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2924.4</c:v>
+                  <c:v>1222.5999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5294.2</c:v>
+                  <c:v>1731.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1703,7 +1718,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0.0</c:v>
+                  <c:v>Deep NUGP, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1760,16 +1775,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-1.5841712617580279</c:v>
+                  <c:v>0.26856957508919888</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-2.5315116791538119</c:v>
+                  <c:v>9.0568532393124776E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-3.058020948180816</c:v>
+                  <c:v>3.2524807056229357E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-3.154452690166976</c:v>
+                  <c:v>-5.8209647495361838E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1790,7 +1805,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep NUGP, ε = 534</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1847,16 +1862,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.45734674018812843</c:v>
+                  <c:v>0.31495296788842042</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.50771264874394018</c:v>
+                  <c:v>0.16328779197884535</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-1.0151598676957001</c:v>
+                  <c:v>0.15752480705622943</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-2.0694573283858997</c:v>
+                  <c:v>-3.8265306122449772E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2422,7 +2437,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0.0</c:v>
+                  <c:v>Deep NUGP, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2485,16 +2500,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2.1540000000000004</c:v>
+                  <c:v>1.7565999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.1160000000000001</c:v>
+                  <c:v>2.4645999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.5113999999999996</c:v>
+                  <c:v>2.7736000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.2281999999999993</c:v>
+                  <c:v>3.4652000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2515,7 +2530,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep NUGP, ε = 534</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2578,16 +2593,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.92139999999999989</c:v>
+                  <c:v>1.7050000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.6539999999999999</c:v>
+                  <c:v>2.3527999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2.12</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.6926000000000001</c:v>
+                  <c:v>3.3335999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3793,16 +3808,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>5.3149599999999998E-2</c:v>
+                  <c:v>0.10617259999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.1382800000000004E-2</c:v>
+                  <c:v>7.8771999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>3.0726200000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.4440600000000002E-2</c:v>
+                  <c:v>0.10128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4485,7 +4500,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0.0</c:v>
+                  <c:v>Deep NUGP, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4572,7 +4587,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε =  5</c:v>
+                  <c:v>Deep NUGP, ε =  534</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4629,16 +4644,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>5.2207999999999997E-2</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.4740000000000002E-2</c:v>
+                  <c:v>0.1197</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>3.4160000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.4948000000000006E-2</c:v>
+                  <c:v>6.7047999999999996E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5329,7 +5344,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0.0</c:v>
+                  <c:v>Deep NUGP, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5416,7 +5431,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε =  5</c:v>
+                  <c:v>Deep NUGP, ε =  534</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5672,68 +5687,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Percentage of Decline</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -6179,16 +6132,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>666</c:v>
+                  <c:v>11.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1555.4</c:v>
+                  <c:v>65.400000000000006</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3059.6</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3609.6</c:v>
+                  <c:v>129.80000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6272,16 +6225,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>6.4</c:v>
+                  <c:v>14.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>560.4</c:v>
+                  <c:v>70.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1261.4000000000001</c:v>
+                  <c:v>103.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2155.6</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11543,7 +11496,7 @@
         <v>24</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -11569,10 +11522,10 @@
         <v>664</v>
       </c>
       <c r="H5">
-        <v>2294</v>
+        <v>467</v>
       </c>
       <c r="I5">
-        <v>308</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -11598,10 +11551,10 @@
         <v>628</v>
       </c>
       <c r="H6">
-        <v>2317</v>
+        <v>456</v>
       </c>
       <c r="I6">
-        <v>336</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -11627,10 +11580,10 @@
         <v>602</v>
       </c>
       <c r="H7">
-        <v>693</v>
+        <v>413</v>
       </c>
       <c r="I7">
-        <v>331</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -11656,10 +11609,10 @@
         <v>591</v>
       </c>
       <c r="H8">
-        <v>1970</v>
+        <v>489</v>
       </c>
       <c r="I8">
-        <v>327</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -11685,10 +11638,10 @@
         <v>598</v>
       </c>
       <c r="H9">
-        <v>693</v>
+        <v>430</v>
       </c>
       <c r="I9">
-        <v>371</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -11742,7 +11695,7 @@
         <v>24</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -11768,10 +11721,10 @@
         <v>811</v>
       </c>
       <c r="H16">
-        <v>3686</v>
+        <v>821</v>
       </c>
       <c r="I16">
-        <v>1285</v>
+        <v>764</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -11797,10 +11750,10 @@
         <v>961</v>
       </c>
       <c r="H17">
-        <v>3262</v>
+        <v>932</v>
       </c>
       <c r="I17">
-        <v>1558</v>
+        <v>719</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -11826,10 +11779,10 @@
         <v>954</v>
       </c>
       <c r="H18">
-        <v>3668</v>
+        <v>869</v>
       </c>
       <c r="I18">
-        <v>1344</v>
+        <v>806</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -11855,10 +11808,10 @@
         <v>955</v>
       </c>
       <c r="H19">
-        <v>3031</v>
+        <v>803</v>
       </c>
       <c r="I19">
-        <v>1586</v>
+        <v>747</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -11884,10 +11837,10 @@
         <v>857</v>
       </c>
       <c r="H20">
-        <v>2379</v>
+        <v>702</v>
       </c>
       <c r="I20">
-        <v>1069</v>
+        <v>761</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -11936,7 +11889,7 @@
         <v>24</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -11962,10 +11915,10 @@
         <v>1630</v>
       </c>
       <c r="H27">
-        <v>6462</v>
+        <v>1574</v>
       </c>
       <c r="I27">
-        <v>3506</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -11991,10 +11944,10 @@
         <v>1293</v>
       </c>
       <c r="H28">
-        <v>4494</v>
+        <v>1394</v>
       </c>
       <c r="I28">
-        <v>1909</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -12020,10 +11973,10 @@
         <v>1450</v>
       </c>
       <c r="H29">
-        <v>5467</v>
+        <v>1348</v>
       </c>
       <c r="I29">
-        <v>3728</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -12049,10 +12002,10 @@
         <v>1465</v>
       </c>
       <c r="H30">
-        <v>6672</v>
+        <v>1269</v>
       </c>
       <c r="I30">
-        <v>3154</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -12078,10 +12031,10 @@
         <v>1418</v>
       </c>
       <c r="H31">
-        <v>6350</v>
+        <v>1435</v>
       </c>
       <c r="I31">
-        <v>2325</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -12130,7 +12083,7 @@
         <v>24</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -12156,10 +12109,10 @@
         <v>1720</v>
       </c>
       <c r="H38">
-        <v>6069</v>
+        <v>1865</v>
       </c>
       <c r="I38">
-        <v>5210</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -12185,10 +12138,10 @@
         <v>1724</v>
       </c>
       <c r="H39">
-        <v>6787</v>
+        <v>1953</v>
       </c>
       <c r="I39">
-        <v>5532</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -12214,10 +12167,10 @@
         <v>1728</v>
       </c>
       <c r="H40">
-        <v>8167</v>
+        <v>1797</v>
       </c>
       <c r="I40">
-        <v>4336</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -12243,10 +12196,10 @@
         <v>1693</v>
       </c>
       <c r="H41">
-        <v>8135</v>
+        <v>1802</v>
       </c>
       <c r="I41">
-        <v>6345</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -12272,10 +12225,10 @@
         <v>1759</v>
       </c>
       <c r="H42">
-        <v>6670</v>
+        <v>1709</v>
       </c>
       <c r="I42">
-        <v>5048</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -12313,7 +12266,7 @@
         <v>24</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -12346,11 +12299,11 @@
       </c>
       <c r="H49">
         <f>AVERAGE(H5:H9)</f>
-        <v>1593.4</v>
+        <v>451</v>
       </c>
       <c r="I49">
         <f>AVERAGE(I5:I9)</f>
-        <v>334.6</v>
+        <v>422.4</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -12383,11 +12336,11 @@
       </c>
       <c r="H50">
         <f>AVERAGE(H16:H20)</f>
-        <v>3205.2</v>
+        <v>825.4</v>
       </c>
       <c r="I50">
         <f>AVERAGE(I16:I20)</f>
-        <v>1368.4</v>
+        <v>759.4</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -12420,11 +12373,11 @@
       </c>
       <c r="H51">
         <f>AVERAGE(H27:H31)</f>
-        <v>5889</v>
+        <v>1404</v>
       </c>
       <c r="I51">
         <f>AVERAGE(I27:I31)</f>
-        <v>2924.4</v>
+        <v>1222.5999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -12457,11 +12410,11 @@
       </c>
       <c r="H52">
         <f>AVERAGE(H38:H42)</f>
-        <v>7165.6</v>
+        <v>1825.2</v>
       </c>
       <c r="I52">
         <f>AVERAGE(I38:I42)</f>
-        <v>5294.2</v>
+        <v>1731.4</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -12472,10 +12425,10 @@
         <v>10</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L57" s="12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -12492,11 +12445,11 @@
       </c>
       <c r="K58" s="13">
         <f>(G49 - H49) / G49</f>
-        <v>-1.5841712617580279</v>
+        <v>0.26856957508919888</v>
       </c>
       <c r="L58" s="13">
         <f>(G49 - I49) / G49</f>
-        <v>0.45734674018812843</v>
+        <v>0.31495296788842042</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -12513,11 +12466,11 @@
       </c>
       <c r="K59" s="13">
         <f t="shared" ref="K59:K61" si="5">(G50 - H50) / G50</f>
-        <v>-2.5315116791538119</v>
+        <v>9.0568532393124776E-2</v>
       </c>
       <c r="L59" s="13">
         <f t="shared" ref="L59:L61" si="6">(G50 - I50) / G50</f>
-        <v>-0.50771264874394018</v>
+        <v>0.16328779197884535</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -12534,11 +12487,11 @@
       </c>
       <c r="K60" s="13">
         <f t="shared" si="5"/>
-        <v>-3.058020948180816</v>
+        <v>3.2524807056229357E-2</v>
       </c>
       <c r="L60" s="13">
         <f t="shared" si="6"/>
-        <v>-1.0151598676957001</v>
+        <v>0.15752480705622943</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -12555,11 +12508,11 @@
       </c>
       <c r="K61" s="13">
         <f t="shared" si="5"/>
-        <v>-3.154452690166976</v>
+        <v>-5.8209647495361838E-2</v>
       </c>
       <c r="L61" s="13">
         <f t="shared" si="6"/>
-        <v>-2.0694573283858997</v>
+        <v>-3.8265306122449772E-3</v>
       </c>
     </row>
   </sheetData>
@@ -12641,7 +12594,7 @@
         <v>24</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -12667,10 +12620,10 @@
         <v>1.5589999999999999</v>
       </c>
       <c r="H4">
-        <v>2.089</v>
+        <v>1.6519999999999999</v>
       </c>
       <c r="I4">
-        <v>0.873</v>
+        <v>1.611</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -12696,10 +12649,10 @@
         <v>1.2150000000000001</v>
       </c>
       <c r="H5">
-        <v>2.5550000000000002</v>
+        <v>1.7729999999999999</v>
       </c>
       <c r="I5">
-        <v>0.86699999999999999</v>
+        <v>1.8140000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -12725,10 +12678,10 @@
         <v>0.96899999999999997</v>
       </c>
       <c r="H6">
-        <v>1.9630000000000001</v>
+        <v>1.6120000000000001</v>
       </c>
       <c r="I6">
-        <v>0.878</v>
+        <v>1.726</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -12754,10 +12707,10 @@
         <v>0.96299999999999997</v>
       </c>
       <c r="H7">
-        <v>2.298</v>
+        <v>1.827</v>
       </c>
       <c r="I7">
-        <v>1.014</v>
+        <v>1.7549999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -12783,10 +12736,10 @@
         <v>1.2649999999999999</v>
       </c>
       <c r="H8">
-        <v>1.865</v>
+        <v>1.919</v>
       </c>
       <c r="I8">
-        <v>0.97499999999999998</v>
+        <v>1.619</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -12861,10 +12814,10 @@
         <v>1.258</v>
       </c>
       <c r="H14">
-        <v>3.3479999999999999</v>
+        <v>2.34</v>
       </c>
       <c r="I14">
-        <v>1.7310000000000001</v>
+        <v>2.1120000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -12890,10 +12843,10 @@
         <v>1.74</v>
       </c>
       <c r="H15">
-        <v>3.585</v>
+        <v>2.2959999999999998</v>
       </c>
       <c r="I15">
-        <v>1.4870000000000001</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -12919,10 +12872,10 @@
         <v>1.3979999999999999</v>
       </c>
       <c r="H16">
-        <v>2.8839999999999999</v>
+        <v>2.3959999999999999</v>
       </c>
       <c r="I16">
-        <v>1.681</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -12948,10 +12901,10 @@
         <v>1.675</v>
       </c>
       <c r="H17">
-        <v>2.9910000000000001</v>
+        <v>2.673</v>
       </c>
       <c r="I17">
-        <v>1.7350000000000001</v>
+        <v>2.496</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -12977,10 +12930,10 @@
         <v>1.365</v>
       </c>
       <c r="H18">
-        <v>2.7719999999999998</v>
+        <v>2.6179999999999999</v>
       </c>
       <c r="I18">
-        <v>1.6359999999999999</v>
+        <v>2.2959999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -13055,7 +13008,7 @@
         <v>2.2970000000000002</v>
       </c>
       <c r="H24">
-        <v>3.6139999999999999</v>
+        <v>2.7639999999999998</v>
       </c>
       <c r="I24">
         <v>2.1619999999999999</v>
@@ -13084,7 +13037,7 @@
         <v>2.4430000000000001</v>
       </c>
       <c r="H25">
-        <v>3.0619999999999998</v>
+        <v>2.794</v>
       </c>
       <c r="I25">
         <v>2.052</v>
@@ -13113,7 +13066,7 @@
         <v>2.3119999999999998</v>
       </c>
       <c r="H26">
-        <v>3.306</v>
+        <v>2.839</v>
       </c>
       <c r="I26">
         <v>2.1389999999999998</v>
@@ -13142,7 +13095,7 @@
         <v>1.946</v>
       </c>
       <c r="H27">
-        <v>3.9510000000000001</v>
+        <v>2.7669999999999999</v>
       </c>
       <c r="I27">
         <v>2.3439999999999999</v>
@@ -13171,7 +13124,7 @@
         <v>1.9550000000000001</v>
       </c>
       <c r="H28">
-        <v>3.6240000000000001</v>
+        <v>2.7040000000000002</v>
       </c>
       <c r="I28">
         <v>1.903</v>
@@ -13249,7 +13202,7 @@
         <v>2.327</v>
       </c>
       <c r="H35">
-        <v>6.09</v>
+        <v>3.4750000000000001</v>
       </c>
       <c r="I35">
         <v>2.6589999999999998</v>
@@ -13278,7 +13231,7 @@
         <v>2.754</v>
       </c>
       <c r="H36">
-        <v>4.6120000000000001</v>
+        <v>3.5790000000000002</v>
       </c>
       <c r="I36">
         <v>3.5209999999999999</v>
@@ -13307,10 +13260,10 @@
         <v>2.7410000000000001</v>
       </c>
       <c r="H37">
-        <v>5.9749999999999996</v>
+        <v>3.3420000000000001</v>
       </c>
       <c r="I37">
-        <v>4.0149999999999997</v>
+        <v>3.3540000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -13336,10 +13289,10 @@
         <v>3.117</v>
       </c>
       <c r="H38">
-        <v>4.5839999999999996</v>
+        <v>3.69</v>
       </c>
       <c r="I38">
-        <v>4.194</v>
+        <v>3.456</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -13365,10 +13318,10 @@
         <v>2.738</v>
       </c>
       <c r="H39">
-        <v>4.88</v>
+        <v>3.24</v>
       </c>
       <c r="I39">
-        <v>4.0739999999999998</v>
+        <v>3.6779999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -13403,10 +13356,10 @@
         <v>10</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -13439,11 +13392,11 @@
       </c>
       <c r="H55">
         <f>AVERAGE(H4:H8)</f>
-        <v>2.1540000000000004</v>
+        <v>1.7565999999999999</v>
       </c>
       <c r="I55">
         <f>AVERAGE(I4:I8)</f>
-        <v>0.92139999999999989</v>
+        <v>1.7050000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -13476,11 +13429,11 @@
       </c>
       <c r="H56">
         <f>AVERAGE(H14:H18)</f>
-        <v>3.1160000000000001</v>
+        <v>2.4645999999999999</v>
       </c>
       <c r="I56">
         <f>AVERAGE(I14:I18)</f>
-        <v>1.6539999999999999</v>
+        <v>2.3527999999999998</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -13513,7 +13466,7 @@
       </c>
       <c r="H57">
         <f>AVERAGE(H24:H28)</f>
-        <v>3.5113999999999996</v>
+        <v>2.7736000000000001</v>
       </c>
       <c r="I57">
         <f>AVERAGE(I24:I28)</f>
@@ -13550,11 +13503,11 @@
       </c>
       <c r="H58">
         <f>AVERAGE(H35:H39)</f>
-        <v>5.2281999999999993</v>
+        <v>3.4652000000000003</v>
       </c>
       <c r="I58">
         <f>AVERAGE(I35:I39)</f>
-        <v>3.6926000000000001</v>
+        <v>3.3335999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -13664,7 +13617,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>5.28E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -13693,7 +13646,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>5.1799999999999999E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -13722,7 +13675,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>5.3499999999999999E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -13751,7 +13704,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>5.2240000000000002E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -13780,7 +13733,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>5.0700000000000002E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -13889,7 +13842,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="5">
-        <v>5.3719999999999997E-2</v>
+        <v>0.10173</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -13906,7 +13859,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="5">
-        <v>5.2769999999999997E-2</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -13923,7 +13876,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="5">
-        <v>5.4480000000000001E-2</v>
+        <v>0.1017</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -13940,7 +13893,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="5">
-        <v>5.3150000000000003E-2</v>
+        <v>0.101733</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -13957,7 +13910,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="5">
-        <v>5.1628E-2</v>
+        <v>0.11070000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -14035,7 +13988,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>5.9700000000000003E-2</v>
+        <v>5.6300000000000003E-2</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -14064,7 +14017,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>3.2300000000000002E-2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -14093,7 +14046,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>5.5399999999999998E-2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -14122,7 +14075,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>3.6299999999999999E-2</v>
+        <v>5.6300000000000003E-2</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -14151,7 +14104,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>0.04</v>
+        <v>0.10589999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -14190,7 +14143,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="5">
-        <v>5.5417000000000001E-2</v>
+        <v>5.6500000000000002E-2</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -14207,7 +14160,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="5">
-        <v>3.0237E-2</v>
+        <v>7.7799999999999994E-2</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -14224,7 +14177,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="5">
-        <v>5.1040000000000002E-2</v>
+        <v>9.1660000000000005E-2</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -14241,7 +14194,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="5">
-        <v>3.3579999999999999E-2</v>
+        <v>5.6500000000000002E-2</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -14258,7 +14211,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="5">
-        <v>3.6639999999999999E-2</v>
+        <v>0.1114</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -14626,7 +14579,7 @@
         <v>24</v>
       </c>
       <c r="I68" s="12" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -14655,7 +14608,7 @@
         <v>0</v>
       </c>
       <c r="I69">
-        <v>2.24E-2</v>
+        <v>3.2899999999999999E-2</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -14816,7 +14769,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="5">
-        <v>3.5060000000000001E-2</v>
+        <v>0.1197</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -14836,7 +14789,7 @@
         <v>0</v>
       </c>
       <c r="F78" s="5">
-        <v>2.2749999999999999E-2</v>
+        <v>0.1048</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -14856,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="5">
-        <v>3.1558000000000003E-2</v>
+        <v>8.4900000000000003E-2</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -14876,7 +14829,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="5">
-        <v>4.5960000000000001E-2</v>
+        <v>0.10249999999999999</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
@@ -14896,7 +14849,7 @@
         <v>0</v>
       </c>
       <c r="F81" s="5">
-        <v>3.6874999999999998E-2</v>
+        <v>9.4500000000000001E-2</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
@@ -14937,10 +14890,10 @@
         <v>10</v>
       </c>
       <c r="L87" s="11" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="M87" s="12" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
@@ -14955,10 +14908,10 @@
         <v>6</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F88" s="12" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I88" s="10">
         <v>2</v>
@@ -14996,7 +14949,7 @@
       </c>
       <c r="F89">
         <f>AVERAGE(I4:I8)</f>
-        <v>5.2207999999999997E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I89" s="1">
         <v>4</v>
@@ -15034,7 +14987,7 @@
       </c>
       <c r="F90">
         <f>AVERAGE(I32:I36)</f>
-        <v>4.4740000000000002E-2</v>
+        <v>0.1197</v>
       </c>
       <c r="I90" s="1">
         <v>8</v>
@@ -15112,7 +15065,7 @@
       </c>
       <c r="F92">
         <f>AVERAGE(I69:I73)</f>
-        <v>6.4948000000000006E-2</v>
+        <v>6.7047999999999996E-2</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
@@ -15133,7 +15086,7 @@
         <v>6</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F96" s="12" t="s">
         <v>26</v>
@@ -15159,7 +15112,7 @@
       </c>
       <c r="F97" s="5">
         <f>AVERAGE(E21:E25)</f>
-        <v>5.3149599999999998E-2</v>
+        <v>0.10617259999999999</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -15182,7 +15135,7 @@
       </c>
       <c r="F98" s="5">
         <f>AVERAGE(E40:E44)</f>
-        <v>4.1382800000000004E-2</v>
+        <v>7.8771999999999995E-2</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -15230,7 +15183,7 @@
       </c>
       <c r="F100" s="5">
         <f>AVERAGE(F77:F81)</f>
-        <v>3.4440600000000002E-2</v>
+        <v>0.10128</v>
       </c>
     </row>
   </sheetData>
@@ -15345,10 +15298,10 @@
         <v>71</v>
       </c>
       <c r="H5" s="6">
-        <v>1082</v>
+        <v>7</v>
       </c>
       <c r="I5" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -15374,10 +15327,10 @@
         <v>46</v>
       </c>
       <c r="H6" s="6">
-        <v>1201</v>
+        <v>7</v>
       </c>
       <c r="I6" s="6">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -15403,10 +15356,10 @@
         <v>56</v>
       </c>
       <c r="H7" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I7" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -15432,10 +15385,10 @@
         <v>63</v>
       </c>
       <c r="H8" s="6">
-        <v>1027</v>
+        <v>23</v>
       </c>
       <c r="I8" s="6">
-        <v>3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -15461,10 +15414,10 @@
         <v>29</v>
       </c>
       <c r="H9" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I9" s="6">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15539,10 +15492,10 @@
         <v>25</v>
       </c>
       <c r="H15">
-        <v>1763</v>
+        <v>36</v>
       </c>
       <c r="I15">
-        <v>544</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -15568,10 +15521,10 @@
         <v>65</v>
       </c>
       <c r="H16">
-        <v>1498</v>
+        <v>90</v>
       </c>
       <c r="I16">
-        <v>641</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -15597,10 +15550,10 @@
         <v>42</v>
       </c>
       <c r="H17">
-        <v>1860</v>
+        <v>22</v>
       </c>
       <c r="I17">
-        <v>671</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -15626,10 +15579,10 @@
         <v>49</v>
       </c>
       <c r="H18">
-        <v>1604</v>
+        <v>96</v>
       </c>
       <c r="I18">
-        <v>644</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -15655,10 +15608,10 @@
         <v>39</v>
       </c>
       <c r="H19">
-        <v>1052</v>
+        <v>83</v>
       </c>
       <c r="I19">
-        <v>302</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -15733,10 +15686,10 @@
         <v>275</v>
       </c>
       <c r="H29">
-        <v>3513</v>
+        <v>102</v>
       </c>
       <c r="I29">
-        <v>1387</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -15762,10 +15715,10 @@
         <v>188</v>
       </c>
       <c r="H30">
-        <v>2369</v>
+        <v>41</v>
       </c>
       <c r="I30">
-        <v>728</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -15791,10 +15744,10 @@
         <v>175</v>
       </c>
       <c r="H31">
-        <v>2776</v>
+        <v>51</v>
       </c>
       <c r="I31">
-        <v>1751</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -15820,10 +15773,10 @@
         <v>249</v>
       </c>
       <c r="H32">
-        <v>3342</v>
+        <v>67</v>
       </c>
       <c r="I32">
-        <v>1333</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -15849,10 +15802,10 @@
         <v>119</v>
       </c>
       <c r="H33">
-        <v>3298</v>
+        <v>54</v>
       </c>
       <c r="I33">
-        <v>1108</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -15927,10 +15880,10 @@
         <v>139</v>
       </c>
       <c r="H41">
-        <v>3332</v>
+        <v>130</v>
       </c>
       <c r="I41">
-        <v>2138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -15956,10 +15909,10 @@
         <v>61</v>
       </c>
       <c r="H42">
-        <v>3500</v>
+        <v>134</v>
       </c>
       <c r="I42">
-        <v>2508</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -15985,10 +15938,10 @@
         <v>90</v>
       </c>
       <c r="H43">
-        <v>4799</v>
+        <v>142</v>
       </c>
       <c r="I43">
-        <v>1553</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -16014,10 +15967,10 @@
         <v>157</v>
       </c>
       <c r="H44">
-        <v>3784</v>
+        <v>124</v>
       </c>
       <c r="I44">
-        <v>2526</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -16043,10 +15996,10 @@
         <v>119</v>
       </c>
       <c r="H45">
-        <v>2633</v>
+        <v>119</v>
       </c>
       <c r="I45">
-        <v>2053</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -16081,7 +16034,7 @@
         <v>10</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I50" s="12" t="s">
         <v>26</v>
@@ -16117,11 +16070,11 @@
       </c>
       <c r="H51">
         <f>AVERAGE(H5:H9)</f>
-        <v>666</v>
+        <v>11.4</v>
       </c>
       <c r="I51">
         <f>AVERAGE(I5:I9)</f>
-        <v>6.4</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -16154,11 +16107,11 @@
       </c>
       <c r="H52">
         <f>AVERAGE(H15:H19)</f>
-        <v>1555.4</v>
+        <v>65.400000000000006</v>
       </c>
       <c r="I52">
         <f>AVERAGE(I15:I19)</f>
-        <v>560.4</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -16191,11 +16144,11 @@
       </c>
       <c r="H53">
         <f>AVERAGE(H29:H33)</f>
-        <v>3059.6</v>
+        <v>63</v>
       </c>
       <c r="I53">
         <f>AVERAGE(I29:I33)</f>
-        <v>1261.4000000000001</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -16228,11 +16181,11 @@
       </c>
       <c r="H54">
         <f>AVERAGE(H41:H45)</f>
-        <v>3609.6</v>
+        <v>129.80000000000001</v>
       </c>
       <c r="I54">
         <f>AVERAGE(I41:I45)</f>
-        <v>2155.6</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments data/K Size/K_Size_PGP_Graph.xlsx
+++ b/Experiments data/K Size/K_Size_PGP_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\K Size\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBE1FD6-8BC9-489B-96C7-3976265C143C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC2F17D-9E88-4FE9-87B0-49109F2A60AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="35">
   <si>
     <t>KaMinPar</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>Deep NUGP, ε =  534</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε relaxed</t>
   </si>
 </sst>
 </file>
@@ -719,7 +722,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 534</c:v>
+                  <c:v>Deep NUGP, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2530,7 +2533,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep NUGP, ε = 534</c:v>
+                  <c:v>Deep NUGP, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4380,7 +4383,7 @@
             <c:numRef>
               <c:f>CCM!$B$89:$B$92</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>0.14455999999999999</c:v>
@@ -4467,7 +4470,7 @@
             <c:numRef>
               <c:f>CCM!$C$89:$C$92</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>0.16008</c:v>
@@ -4554,7 +4557,7 @@
             <c:numRef>
               <c:f>CCM!$E$89:$E$92</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -4587,7 +4590,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep NUGP, ε =  534</c:v>
+                  <c:v>Deep NUGP, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4641,7 +4644,7 @@
             <c:numRef>
               <c:f>CCM!$F$89:$F$92</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>0.1</c:v>
@@ -4759,7 +4762,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
-                      <c:formatCode>General</c:formatCode>
+                      <c:formatCode>0%</c:formatCode>
                       <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>0</c:v>
@@ -4955,7 +4958,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -12266,7 +12269,7 @@
         <v>24</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -13359,7 +13362,7 @@
         <v>31</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -14911,7 +14914,7 @@
         <v>31</v>
       </c>
       <c r="F88" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I88" s="10">
         <v>2</v>
@@ -14933,21 +14936,21 @@
       <c r="A89" s="10">
         <v>2</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="13">
         <f>AVERAGE(F4:F8)</f>
         <v>0.14455999999999999</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="13">
         <f>AVERAGE(G4:G8)</f>
         <v>0.16008</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="13">
         <v>0</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="13">
         <v>0</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="13">
         <f>AVERAGE(I4:I8)</f>
         <v>0.1</v>
       </c>
@@ -14971,21 +14974,21 @@
       <c r="A90" s="1">
         <v>4</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="13">
         <f>AVERAGE(F32:F36)</f>
         <v>0.26247999999999999</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="13">
         <f>AVERAGE(G32:G36)</f>
         <v>0.27643999999999996</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="13">
         <v>0</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="13">
         <v>0</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="13">
         <f>AVERAGE(I32:I36)</f>
         <v>0.1197</v>
       </c>
@@ -15009,22 +15012,22 @@
       <c r="A91" s="1">
         <v>8</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="13">
         <f>AVERAGE(F50:F54)</f>
         <v>0.49659999999999993</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="13">
         <f>AVERAGE(G50:G54)</f>
         <v>0.51260000000000006</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="13">
         <f>AVERAGE(B50:B54)</f>
         <v>6.0600000000000003E-3</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="13">
         <v>0</v>
       </c>
-      <c r="F91">
+      <c r="F91" s="13">
         <f>AVERAGE(I50:I54)</f>
         <v>3.4160000000000003E-2</v>
       </c>
@@ -15048,22 +15051,22 @@
       <c r="A92" s="1">
         <v>16</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="13">
         <f>AVERAGE(F69:F73)</f>
         <v>0.85804000000000014</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="13">
         <f>AVERAGE(G69:G73)</f>
         <v>0.87674000000000007</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="13">
         <f>AVERAGE(B69:B73)</f>
         <v>6.1968000000000002E-2</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="13">
         <v>0</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="13">
         <f>AVERAGE(I69:I73)</f>
         <v>6.7047999999999996E-2</v>
       </c>

--- a/Experiments data/K Size/K_Size_PGP_Graph.xlsx
+++ b/Experiments data/K Size/K_Size_PGP_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\K Size\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBE1FD6-8BC9-489B-96C7-3976265C143C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901B7AB9-C2A7-4617-BF87-53D43B707CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="34">
   <si>
     <t>KaMinPar</t>
   </si>
@@ -329,17 +329,17 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -12535,7 +12535,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:R58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -13324,7 +13324,7 @@
         <v>3.6779999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
         <v>22</v>
       </c>
@@ -13335,7 +13335,7 @@
       <c r="F53" s="16"/>
       <c r="G53" s="16"/>
     </row>
-    <row r="54" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="1" t="s">
         <v>6</v>
@@ -13361,8 +13361,21 @@
       <c r="I54" s="12" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="N54" s="2"/>
+      <c r="O54" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q54" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="R54" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>2</v>
       </c>
@@ -13398,8 +13411,23 @@
         <f>AVERAGE(I4:I8)</f>
         <v>1.7050000000000001</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="N55" s="1">
+        <v>2</v>
+      </c>
+      <c r="O55">
+        <v>0.97059999999999991</v>
+      </c>
+      <c r="P55">
+        <v>1.1941999999999999</v>
+      </c>
+      <c r="Q55">
+        <v>1.7565999999999999</v>
+      </c>
+      <c r="R55">
+        <v>1.7050000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>4</v>
       </c>
@@ -13435,8 +13463,23 @@
         <f>AVERAGE(I14:I18)</f>
         <v>2.3527999999999998</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="N56" s="1">
+        <v>4</v>
+      </c>
+      <c r="O56">
+        <v>1.5190000000000001</v>
+      </c>
+      <c r="P56">
+        <v>1.4872000000000001</v>
+      </c>
+      <c r="Q56">
+        <v>2.4645999999999999</v>
+      </c>
+      <c r="R56">
+        <v>2.3527999999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>8</v>
       </c>
@@ -13472,8 +13515,23 @@
         <f>AVERAGE(I24:I28)</f>
         <v>2.12</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="N57" s="1">
+        <v>8</v>
+      </c>
+      <c r="O57">
+        <v>2.0973999999999999</v>
+      </c>
+      <c r="P57">
+        <v>2.1905999999999999</v>
+      </c>
+      <c r="Q57">
+        <v>2.7736000000000001</v>
+      </c>
+      <c r="R57">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>16</v>
       </c>
@@ -13507,6 +13565,21 @@
       </c>
       <c r="I58">
         <f>AVERAGE(I35:I39)</f>
+        <v>3.3335999999999997</v>
+      </c>
+      <c r="N58" s="1">
+        <v>16</v>
+      </c>
+      <c r="O58">
+        <v>2.3555999999999999</v>
+      </c>
+      <c r="P58">
+        <v>2.7353999999999998</v>
+      </c>
+      <c r="Q58">
+        <v>3.4652000000000003</v>
+      </c>
+      <c r="R58">
         <v>3.3335999999999997</v>
       </c>
     </row>
@@ -13737,11 +13810,11 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -14215,15 +14288,15 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="19" t="s">
+      <c r="A47" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
@@ -14534,15 +14607,15 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="19" t="s">
+      <c r="A66" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B66" s="19"/>
-      <c r="C66" s="19"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="19"/>
-      <c r="F66" s="19"/>
-      <c r="G66" s="19"/>
+      <c r="B66" s="20"/>
+      <c r="C66" s="20"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="15" t="s">
@@ -15069,11 +15142,11 @@
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A95" s="20" t="s">
+      <c r="A95" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B95" s="20"/>
-      <c r="C95" s="20"/>
+      <c r="B95" s="17"/>
+      <c r="C95" s="17"/>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
@@ -15188,11 +15261,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A75:C75"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A11:C11"/>
@@ -15204,6 +15272,11 @@
     <mergeCell ref="A47:G47"/>
     <mergeCell ref="A48:G48"/>
     <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A86:G86"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A75:C75"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15615,15 +15688,15 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
@@ -15809,15 +15882,15 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">

--- a/Experiments data/K Size/K_Size_PGP_Graph.xlsx
+++ b/Experiments data/K Size/K_Size_PGP_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\K Size\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901B7AB9-C2A7-4617-BF87-53D43B707CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBE1FD6-8BC9-489B-96C7-3976265C143C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="34">
   <si>
     <t>KaMinPar</t>
   </si>
@@ -329,17 +329,17 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -12535,7 +12535,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R58"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -13324,7 +13324,7 @@
         <v>3.6779999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
         <v>22</v>
       </c>
@@ -13335,7 +13335,7 @@
       <c r="F53" s="16"/>
       <c r="G53" s="16"/>
     </row>
-    <row r="54" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="1" t="s">
         <v>6</v>
@@ -13361,21 +13361,8 @@
       <c r="I54" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P54" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q54" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="R54" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>2</v>
       </c>
@@ -13411,23 +13398,8 @@
         <f>AVERAGE(I4:I8)</f>
         <v>1.7050000000000001</v>
       </c>
-      <c r="N55" s="1">
-        <v>2</v>
-      </c>
-      <c r="O55">
-        <v>0.97059999999999991</v>
-      </c>
-      <c r="P55">
-        <v>1.1941999999999999</v>
-      </c>
-      <c r="Q55">
-        <v>1.7565999999999999</v>
-      </c>
-      <c r="R55">
-        <v>1.7050000000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>4</v>
       </c>
@@ -13463,23 +13435,8 @@
         <f>AVERAGE(I14:I18)</f>
         <v>2.3527999999999998</v>
       </c>
-      <c r="N56" s="1">
-        <v>4</v>
-      </c>
-      <c r="O56">
-        <v>1.5190000000000001</v>
-      </c>
-      <c r="P56">
-        <v>1.4872000000000001</v>
-      </c>
-      <c r="Q56">
-        <v>2.4645999999999999</v>
-      </c>
-      <c r="R56">
-        <v>2.3527999999999998</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>8</v>
       </c>
@@ -13515,23 +13472,8 @@
         <f>AVERAGE(I24:I28)</f>
         <v>2.12</v>
       </c>
-      <c r="N57" s="1">
-        <v>8</v>
-      </c>
-      <c r="O57">
-        <v>2.0973999999999999</v>
-      </c>
-      <c r="P57">
-        <v>2.1905999999999999</v>
-      </c>
-      <c r="Q57">
-        <v>2.7736000000000001</v>
-      </c>
-      <c r="R57">
-        <v>2.12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>16</v>
       </c>
@@ -13565,21 +13507,6 @@
       </c>
       <c r="I58">
         <f>AVERAGE(I35:I39)</f>
-        <v>3.3335999999999997</v>
-      </c>
-      <c r="N58" s="1">
-        <v>16</v>
-      </c>
-      <c r="O58">
-        <v>2.3555999999999999</v>
-      </c>
-      <c r="P58">
-        <v>2.7353999999999998</v>
-      </c>
-      <c r="Q58">
-        <v>3.4652000000000003</v>
-      </c>
-      <c r="R58">
         <v>3.3335999999999997</v>
       </c>
     </row>
@@ -13810,11 +13737,11 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -14288,15 +14215,15 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="20" t="s">
+      <c r="A47" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B47" s="20"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
@@ -14607,15 +14534,15 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="20" t="s">
+      <c r="A66" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B66" s="20"/>
-      <c r="C66" s="20"/>
-      <c r="D66" s="20"/>
-      <c r="E66" s="20"/>
-      <c r="F66" s="20"/>
-      <c r="G66" s="20"/>
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="15" t="s">
@@ -15142,11 +15069,11 @@
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A95" s="17" t="s">
+      <c r="A95" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B95" s="17"/>
-      <c r="C95" s="17"/>
+      <c r="B95" s="20"/>
+      <c r="C95" s="20"/>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
@@ -15261,6 +15188,11 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A86:G86"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A75:C75"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A11:C11"/>
@@ -15272,11 +15204,6 @@
     <mergeCell ref="A47:G47"/>
     <mergeCell ref="A48:G48"/>
     <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A75:C75"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15688,15 +15615,15 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
@@ -15882,15 +15809,15 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
